--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104000150</v>
+        <v>136859176</v>
       </c>
       <c r="B2" t="n">
-        <v>93213</v>
+        <v>79508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546138</v>
+        <v>546217</v>
       </c>
       <c r="R2" t="n">
-        <v>6960629</v>
+        <v>6960586</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,78 +771,69 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000150</t>
+          <t>https://artportalen.se/Sighting/136859176</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104000148</v>
+        <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>93189</v>
+        <v>92292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546103</v>
+        <v>546095</v>
       </c>
       <c r="R3" t="n">
-        <v>6960555</v>
+        <v>6960561</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,62 +883,53 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000148</t>
+          <t>https://artportalen.se/Sighting/136859182</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104000149</v>
+        <v>104000150</v>
       </c>
       <c r="B4" t="n">
-        <v>93191</v>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546132</v>
+        <v>546138</v>
       </c>
       <c r="R4" t="n">
-        <v>6960563</v>
+        <v>6960629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,54 +1019,54 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000149</t>
+          <t>https://artportalen.se/Sighting/104000150</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104000191</v>
+        <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>93191</v>
+        <v>96565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546053</v>
+        <v>546147</v>
       </c>
       <c r="R5" t="n">
-        <v>6960561</v>
+        <v>6960436</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1090,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,40 +1116,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000191</t>
+          <t>https://artportalen.se/Sighting/136859183</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369922</v>
+        <v>104000148</v>
       </c>
       <c r="B6" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,41 +1148,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546230</v>
+        <v>546103</v>
       </c>
       <c r="R6" t="n">
-        <v>6960563</v>
+        <v>6960555</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,12 +1202,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,31 +1228,40 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369922</t>
+          <t>https://artportalen.se/Sighting/104000148</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369924</v>
+        <v>104000149</v>
       </c>
       <c r="B7" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,41 +1269,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546160</v>
+        <v>546132</v>
       </c>
       <c r="R7" t="n">
-        <v>6960602</v>
+        <v>6960563</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,12 +1323,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,53 +1349,62 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369924</t>
+          <t>https://artportalen.se/Sighting/104000149</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104000144</v>
+        <v>104000191</v>
       </c>
       <c r="B8" t="n">
-        <v>93201</v>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546137</v>
+        <v>546053</v>
       </c>
       <c r="R8" t="n">
-        <v>6960630</v>
+        <v>6960561</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,16 +1494,16 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000144</t>
+          <t>https://artportalen.se/Sighting/104000191</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104000180</v>
+        <v>128369922</v>
       </c>
       <c r="B9" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,37 +1511,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546069</v>
+        <v>546230</v>
       </c>
       <c r="R9" t="n">
-        <v>6960569</v>
+        <v>6960563</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,22 +1569,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,40 +1585,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000180</t>
+          <t>https://artportalen.se/Sighting/128369922</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128369923</v>
+        <v>128369924</v>
       </c>
       <c r="B10" t="n">
-        <v>78730</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,21 +1617,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1657,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546215</v>
+        <v>546160</v>
       </c>
       <c r="R10" t="n">
-        <v>6960568</v>
+        <v>6960602</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1718,7 +1706,1864 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/128369924</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136859175</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>546232</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6960566</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859175</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136859178</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>546159</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6960606</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859178</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136859179</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>546151</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6960612</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859179</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104000144</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>546137</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6960630</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000144</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136859181</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93415</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>546095</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6960561</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859181</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104000180</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>546069</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6960569</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000180</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136859180</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93423</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>546117</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6960567</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859180</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136859185</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93083</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>546144</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6960426</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859185</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136859190</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93083</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>546132</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6960426</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859190</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136859191</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93083</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>546122</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6960432</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859191</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136859173</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>546190</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6960431</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859173</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136859174</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>546238</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6960563</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Stor garnlavsbål på tall. 30vm lång. Välmående med apotecier</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859174</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128369923</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>546215</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6960568</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128369923</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136859177</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>546156</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6960571</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859177</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136859184</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99691</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>546146</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6960434</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859184</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136859187</v>
+      </c>
+      <c r="B26" t="n">
+        <v>104876</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>546141</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6960424</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859187</t>
         </is>
       </c>
     </row>
@@ -1733,6 +3578,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859176</v>
       </c>
       <c r="B2" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>136859173</v>
       </c>
       <c r="B21" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>136859174</v>
       </c>
       <c r="B22" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136859177</v>
       </c>
       <c r="B24" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99691</v>
+        <v>99697</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859176</v>
       </c>
       <c r="B2" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>136859173</v>
       </c>
       <c r="B21" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>136859174</v>
       </c>
       <c r="B22" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136859177</v>
       </c>
       <c r="B24" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99697</v>
+        <v>99699</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859176</v>
       </c>
       <c r="B2" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>136859173</v>
       </c>
       <c r="B21" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>136859174</v>
       </c>
       <c r="B22" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136859177</v>
       </c>
       <c r="B24" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99699</v>
+        <v>99700</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99700</v>
+        <v>99706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859176</v>
       </c>
       <c r="B2" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>136859173</v>
       </c>
       <c r="B21" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>136859174</v>
       </c>
       <c r="B22" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136859177</v>
       </c>
       <c r="B24" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99706</v>
+        <v>99710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99710</v>
+        <v>99712</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859176</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>136859173</v>
       </c>
       <c r="B21" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>136859174</v>
       </c>
       <c r="B22" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136859177</v>
       </c>
       <c r="B24" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99712</v>
+        <v>99714</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859176</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>136859173</v>
       </c>
       <c r="B21" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>136859174</v>
       </c>
       <c r="B22" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136859177</v>
       </c>
       <c r="B24" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99714</v>
+        <v>99727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859176</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>136859173</v>
       </c>
       <c r="B21" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>136859174</v>
       </c>
       <c r="B22" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136859177</v>
       </c>
       <c r="B24" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99727</v>
+        <v>99729</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99729</v>
+        <v>99732</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859176</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>136859173</v>
       </c>
       <c r="B21" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>136859174</v>
       </c>
       <c r="B22" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136859177</v>
       </c>
       <c r="B24" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99732</v>
+        <v>99742</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99742</v>
+        <v>99743</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859176</v>
       </c>
       <c r="B2" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>136859173</v>
       </c>
       <c r="B21" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>136859174</v>
       </c>
       <c r="B22" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136859177</v>
       </c>
       <c r="B24" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99743</v>
+        <v>99748</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99748</v>
+        <v>99751</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859176</v>
       </c>
       <c r="B2" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>136859173</v>
       </c>
       <c r="B21" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>136859174</v>
       </c>
       <c r="B22" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136859177</v>
       </c>
       <c r="B24" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99751</v>
+        <v>99757</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 62113-2023 artfynd.xlsx
+++ b/artfynd/A 62113-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136859176</v>
       </c>
       <c r="B2" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136859182</v>
       </c>
       <c r="B3" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136859183</v>
       </c>
       <c r="B5" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>136859175</v>
       </c>
       <c r="B11" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>136859178</v>
       </c>
       <c r="B12" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136859179</v>
       </c>
       <c r="B13" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>136859181</v>
       </c>
       <c r="B15" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136859180</v>
       </c>
       <c r="B17" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>136859185</v>
       </c>
       <c r="B18" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136859190</v>
       </c>
       <c r="B19" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136859191</v>
       </c>
       <c r="B20" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>136859173</v>
       </c>
       <c r="B21" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>136859174</v>
       </c>
       <c r="B22" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136859177</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136859184</v>
       </c>
       <c r="B25" t="n">
-        <v>99757</v>
+        <v>99769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>136859187</v>
       </c>
       <c r="B26" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
